--- a/api-discoveries/reports/REACH_DataCite_Date_Reconciliation_Historical_2026-10-28.xlsx
+++ b/api-discoveries/reports/REACH_DataCite_Date_Reconciliation_Historical_2026-10-28.xlsx
@@ -5,7 +5,7 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Date Reconciliation" sheetId="2" r:id="rId2"/>
     <sheet name="Repository Breakdown" sheetId="3" r:id="rId3"/>
-    <sheet name="Needs Reviewer Check" sheetId="4" r:id="rId4"/>
+    <sheet name="Optional Date Evidence" sheetId="4" r:id="rId4"/>
     <sheet name="Read Me" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
@@ -163,7 +163,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOI created/registered date only — candidate, not publication</t>
+          <t xml:space="preserve">DOI-created/registered only (research evidence; not a REACH Pub Date blocker)</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -183,7 +183,7 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conflicting dates requiring individual review</t>
+          <t xml:space="preserve">Conflicting publication histories (informational, not Pub Date blockers)</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -193,41 +193,61 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Original source manifest SHA-256</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">b21e3b81cf47c3187eb851d1d2b5ec0200d8ed54970c01f871bbd8b96475921e</t>
-        </is>
+          <t xml:space="preserve">REACH Pub Date satisfied under office created-date policy</t>
+        </is>
+      </c>
+      <c r="B13" s="2">
+        <v>188</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DataCite date semantics</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">created = DOI record created; registered = DOI became registered; published = Issued or fallback publication year; updated = metadata change</t>
-        </is>
+          <t xml:space="preserve">Still missing REACH Pub Date (no valid DataCite created)</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">Original source manifest SHA-256</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">b21e3b81cf47c3187eb851d1d2b5ec0200d8ed54970c01f871bbd8b96475921e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DataCite date semantics</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">created = DOI record created; registered = DOI became registered; published = Issued or fallback publication year; updated = metadata change</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">REACH publication dates modified</t>
         </is>
       </c>
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">NONE — all proposed dates remain separate, no automated approval</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -256,10 +276,12 @@
     <col min="19" max="19" width="23" customWidth="1"/>
     <col min="20" max="20" width="25" customWidth="1"/>
     <col min="21" max="21" width="96" customWidth="1"/>
-    <col min="22" max="22" width="55" customWidth="1"/>
-    <col min="23" max="23" width="38" customWidth="1"/>
-    <col min="24" max="24" width="67" customWidth="1"/>
-    <col min="25" max="25" width="78" customWidth="1"/>
+    <col min="22" max="22" width="27" customWidth="1"/>
+    <col min="23" max="23" width="40" customWidth="1"/>
+    <col min="24" max="24" width="55" customWidth="1"/>
+    <col min="25" max="25" width="38" customWidth="1"/>
+    <col min="26" max="26" width="67" customWidth="1"/>
+    <col min="27" max="27" width="78" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -370,20 +392,30 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH Pub Date (DataCite created; editable)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH Pub Date Source</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Related Version DOI(s)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">API Retrieval</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">DataCite Evidence URL</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Source Batch</t>
         </is>
@@ -497,20 +529,30 @@
       </c>
       <c r="V2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-12-17</t>
         </is>
       </c>
       <c r="W2" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y2" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X2" s="0" t="inlineStr">
+      <c r="Z2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.13012/b2idb-0704763_v1</t>
         </is>
       </c>
-      <c r="Y2" s="0" t="inlineStr">
+      <c r="AA2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -624,20 +666,30 @@
       </c>
       <c r="V3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-29</t>
         </is>
       </c>
       <c r="W3" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y3" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X3" s="0" t="inlineStr">
+      <c r="Z3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.15139/s3/uy6rda</t>
         </is>
       </c>
-      <c r="Y3" s="0" t="inlineStr">
+      <c r="AA3" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -751,20 +803,30 @@
       </c>
       <c r="V4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-06-29</t>
         </is>
       </c>
       <c r="W4" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y4" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X4" s="0" t="inlineStr">
+      <c r="Z4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-05s8-ah21</t>
         </is>
       </c>
-      <c r="Y4" s="0" t="inlineStr">
+      <c r="AA4" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -878,20 +940,30 @@
       </c>
       <c r="V5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-10-23</t>
         </is>
       </c>
       <c r="W5" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y5" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X5" s="0" t="inlineStr">
+      <c r="Z5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-0fwc-wy13</t>
         </is>
       </c>
-      <c r="Y5" s="0" t="inlineStr">
+      <c r="AA5" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -1005,20 +1077,30 @@
       </c>
       <c r="V6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="W6" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y6" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X6" s="0" t="inlineStr">
+      <c r="Z6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-4zfp-8h65</t>
         </is>
       </c>
-      <c r="Y6" s="0" t="inlineStr">
+      <c r="AA6" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -1132,20 +1214,30 @@
       </c>
       <c r="V7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="W7" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y7" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X7" s="0" t="inlineStr">
+      <c r="Z7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-54v5-z541</t>
         </is>
       </c>
-      <c r="Y7" s="0" t="inlineStr">
+      <c r="AA7" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -1259,20 +1351,30 @@
       </c>
       <c r="V8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-04-10</t>
         </is>
       </c>
       <c r="W8" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y8" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X8" s="0" t="inlineStr">
+      <c r="Z8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-58ft-kp27</t>
         </is>
       </c>
-      <c r="Y8" s="0" t="inlineStr">
+      <c r="AA8" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -1386,20 +1488,30 @@
       </c>
       <c r="V9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-05-23</t>
         </is>
       </c>
       <c r="W9" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y9" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X9" s="0" t="inlineStr">
+      <c r="Z9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-66t0-a761</t>
         </is>
       </c>
-      <c r="Y9" s="0" t="inlineStr">
+      <c r="AA9" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -1513,20 +1625,30 @@
       </c>
       <c r="V10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-04-14</t>
         </is>
       </c>
       <c r="W10" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y10" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X10" s="0" t="inlineStr">
+      <c r="Z10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-6g47-4387</t>
         </is>
       </c>
-      <c r="Y10" s="0" t="inlineStr">
+      <c r="AA10" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -1640,20 +1762,30 @@
       </c>
       <c r="V11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-04-10</t>
         </is>
       </c>
       <c r="W11" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y11" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X11" s="0" t="inlineStr">
+      <c r="Z11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-6vmm-2g61</t>
         </is>
       </c>
-      <c r="Y11" s="0" t="inlineStr">
+      <c r="AA11" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -1767,20 +1899,30 @@
       </c>
       <c r="V12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-10-23</t>
         </is>
       </c>
       <c r="W12" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y12" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X12" s="0" t="inlineStr">
+      <c r="Z12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-967n-t829</t>
         </is>
       </c>
-      <c r="Y12" s="0" t="inlineStr">
+      <c r="AA12" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -1894,20 +2036,30 @@
       </c>
       <c r="V13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-06-06</t>
         </is>
       </c>
       <c r="W13" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y13" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X13" s="0" t="inlineStr">
+      <c r="Z13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-9jv0-9m71</t>
         </is>
       </c>
-      <c r="Y13" s="0" t="inlineStr">
+      <c r="AA13" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -2021,20 +2173,30 @@
       </c>
       <c r="V14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-06-04</t>
         </is>
       </c>
       <c r="W14" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y14" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X14" s="0" t="inlineStr">
+      <c r="Z14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-bpav-8w29</t>
         </is>
       </c>
-      <c r="Y14" s="0" t="inlineStr">
+      <c r="AA14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -2148,20 +2310,30 @@
       </c>
       <c r="V15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="W15" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y15" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X15" s="0" t="inlineStr">
+      <c r="Z15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-crsw-jr87</t>
         </is>
       </c>
-      <c r="Y15" s="0" t="inlineStr">
+      <c r="AA15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -2275,20 +2447,30 @@
       </c>
       <c r="V16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-04-14</t>
         </is>
       </c>
       <c r="W16" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y16" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X16" s="0" t="inlineStr">
+      <c r="Z16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-ehfz-ja17</t>
         </is>
       </c>
-      <c r="Y16" s="0" t="inlineStr">
+      <c r="AA16" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -2402,20 +2584,30 @@
       </c>
       <c r="V17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-05-23</t>
         </is>
       </c>
       <c r="W17" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y17" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X17" s="0" t="inlineStr">
+      <c r="Z17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-fhf3-ga95</t>
         </is>
       </c>
-      <c r="Y17" s="0" t="inlineStr">
+      <c r="AA17" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -2529,20 +2721,30 @@
       </c>
       <c r="V18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-04-14</t>
         </is>
       </c>
       <c r="W18" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y18" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X18" s="0" t="inlineStr">
+      <c r="Z18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-gc4p-2m64</t>
         </is>
       </c>
-      <c r="Y18" s="0" t="inlineStr">
+      <c r="AA18" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -2656,20 +2858,30 @@
       </c>
       <c r="V19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-06-29</t>
         </is>
       </c>
       <c r="W19" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y19" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X19" s="0" t="inlineStr">
+      <c r="Z19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-j9hc-xy24</t>
         </is>
       </c>
-      <c r="Y19" s="0" t="inlineStr">
+      <c r="AA19" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -2783,20 +2995,30 @@
       </c>
       <c r="V20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-08-18</t>
         </is>
       </c>
       <c r="W20" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y20" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X20" s="0" t="inlineStr">
+      <c r="Z20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-jfsc-8902</t>
         </is>
       </c>
-      <c r="Y20" s="0" t="inlineStr">
+      <c r="AA20" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -2910,20 +3132,30 @@
       </c>
       <c r="V21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-04-14</t>
         </is>
       </c>
       <c r="W21" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y21" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X21" s="0" t="inlineStr">
+      <c r="Z21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-jmwe-bm11</t>
         </is>
       </c>
-      <c r="Y21" s="0" t="inlineStr">
+      <c r="AA21" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -3037,20 +3269,30 @@
       </c>
       <c r="V22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-06-29</t>
         </is>
       </c>
       <c r="W22" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y22" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X22" s="0" t="inlineStr">
+      <c r="Z22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-n1rz-ak22</t>
         </is>
       </c>
-      <c r="Y22" s="0" t="inlineStr">
+      <c r="AA22" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -3164,20 +3406,30 @@
       </c>
       <c r="V23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-13</t>
         </is>
       </c>
       <c r="W23" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y23" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X23" s="0" t="inlineStr">
+      <c r="Z23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-qar3-zx34</t>
         </is>
       </c>
-      <c r="Y23" s="0" t="inlineStr">
+      <c r="AA23" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -3291,20 +3543,30 @@
       </c>
       <c r="V24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-10-23</t>
         </is>
       </c>
       <c r="W24" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y24" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X24" s="0" t="inlineStr">
+      <c r="Z24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-qm3n-6h83</t>
         </is>
       </c>
-      <c r="Y24" s="0" t="inlineStr">
+      <c r="AA24" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -3418,20 +3680,30 @@
       </c>
       <c r="V25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-05-23</t>
         </is>
       </c>
       <c r="W25" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y25" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X25" s="0" t="inlineStr">
+      <c r="Z25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-rgbs-xd77</t>
         </is>
       </c>
-      <c r="Y25" s="0" t="inlineStr">
+      <c r="AA25" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -3545,20 +3817,30 @@
       </c>
       <c r="V26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-01-26</t>
         </is>
       </c>
       <c r="W26" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y26" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X26" s="0" t="inlineStr">
+      <c r="Z26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-wqy9-rj81</t>
         </is>
       </c>
-      <c r="Y26" s="0" t="inlineStr">
+      <c r="AA26" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -3672,20 +3954,30 @@
       </c>
       <c r="V27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-02-24</t>
         </is>
       </c>
       <c r="W27" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y27" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X27" s="0" t="inlineStr">
+      <c r="Z27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-xjyf-nc93</t>
         </is>
       </c>
-      <c r="Y27" s="0" t="inlineStr">
+      <c r="AA27" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -3799,20 +4091,30 @@
       </c>
       <c r="V28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-04-10</t>
         </is>
       </c>
       <c r="W28" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y28" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X28" s="0" t="inlineStr">
+      <c r="Z28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-ydmk-q397</t>
         </is>
       </c>
-      <c r="Y28" s="0" t="inlineStr">
+      <c r="AA28" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -3926,20 +4228,30 @@
       </c>
       <c r="V29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-01-27</t>
         </is>
       </c>
       <c r="W29" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y29" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X29" s="0" t="inlineStr">
+      <c r="Z29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-yry6-r324</t>
         </is>
       </c>
-      <c r="Y29" s="0" t="inlineStr">
+      <c r="AA29" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -4053,20 +4365,30 @@
       </c>
       <c r="V30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-05-22</t>
         </is>
       </c>
       <c r="W30" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y30" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X30" s="0" t="inlineStr">
+      <c r="Z30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17603/ds2-zb1x-f792</t>
         </is>
       </c>
-      <c r="Y30" s="0" t="inlineStr">
+      <c r="AA30" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -4180,20 +4502,30 @@
       </c>
       <c r="V31" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2023-03-06</t>
+        </is>
+      </c>
+      <c r="W31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X31" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasPart: 10.17605/osf.io/93myk; HasPart: https://osf.io/c4etf; HasPart: 10.17605/osf.io/c7gkw; HasPart: https://osf.io/cn7xa; HasPart: https://osf.io/whq2x</t>
         </is>
       </c>
-      <c r="W31" s="0" t="inlineStr">
+      <c r="Y31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X31" s="0" t="inlineStr">
+      <c r="Z31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17605/osf.io/jr7pv</t>
         </is>
       </c>
-      <c r="Y31" s="0" t="inlineStr">
+      <c r="AA31" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -4307,20 +4639,30 @@
       </c>
       <c r="V32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-11-26</t>
         </is>
       </c>
       <c r="W32" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y32" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X32" s="0" t="inlineStr">
+      <c r="Z32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.17605/osf.io/rbdfv</t>
         </is>
       </c>
-      <c r="Y32" s="0" t="inlineStr">
+      <c r="AA32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -4434,20 +4776,30 @@
       </c>
       <c r="V33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-02-24</t>
         </is>
       </c>
       <c r="W33" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y33" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X33" s="0" t="inlineStr">
+      <c r="Z33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.18738/t8/momo42</t>
         </is>
       </c>
-      <c r="Y33" s="0" t="inlineStr">
+      <c r="AA33" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -4561,20 +4913,30 @@
       </c>
       <c r="V34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-07-22</t>
         </is>
       </c>
       <c r="W34" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y34" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X34" s="0" t="inlineStr">
+      <c r="Z34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25394/pgs.14916606</t>
         </is>
       </c>
-      <c r="Y34" s="0" t="inlineStr">
+      <c r="AA34" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -4688,20 +5050,30 @@
       </c>
       <c r="V35" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2021-07-22</t>
+        </is>
+      </c>
+      <c r="W35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X35" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsIdenticalTo: 10.25394/pgs.14916606</t>
         </is>
       </c>
-      <c r="W35" s="0" t="inlineStr">
+      <c r="Y35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X35" s="0" t="inlineStr">
+      <c r="Z35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25394/pgs.14916606.v1</t>
         </is>
       </c>
-      <c r="Y35" s="0" t="inlineStr">
+      <c r="AA35" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -4815,20 +5187,30 @@
       </c>
       <c r="V36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-07-28</t>
         </is>
       </c>
       <c r="W36" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y36" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X36" s="0" t="inlineStr">
+      <c r="Z36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25394/pgs.20392422</t>
         </is>
       </c>
-      <c r="Y36" s="0" t="inlineStr">
+      <c r="AA36" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -4942,20 +5324,30 @@
       </c>
       <c r="V37" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2022-07-28</t>
+        </is>
+      </c>
+      <c r="W37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X37" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsIdenticalTo: 10.25394/pgs.20392422</t>
         </is>
       </c>
-      <c r="W37" s="0" t="inlineStr">
+      <c r="Y37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X37" s="0" t="inlineStr">
+      <c r="Z37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25394/pgs.20392422.v1</t>
         </is>
       </c>
-      <c r="Y37" s="0" t="inlineStr">
+      <c r="AA37" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -5069,20 +5461,30 @@
       </c>
       <c r="V38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-08-17</t>
         </is>
       </c>
       <c r="W38" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y38" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X38" s="0" t="inlineStr">
+      <c r="Z38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25820/data.006126</t>
         </is>
       </c>
-      <c r="Y38" s="0" t="inlineStr">
+      <c r="AA38" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -5196,20 +5598,30 @@
       </c>
       <c r="V39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-09-20</t>
         </is>
       </c>
       <c r="W39" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y39" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X39" s="0" t="inlineStr">
+      <c r="Z39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25820/data.006144</t>
         </is>
       </c>
-      <c r="Y39" s="0" t="inlineStr">
+      <c r="AA39" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -5323,20 +5735,30 @@
       </c>
       <c r="V40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-18</t>
         </is>
       </c>
       <c r="W40" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y40" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X40" s="0" t="inlineStr">
+      <c r="Z40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/0vz0-ra19</t>
         </is>
       </c>
-      <c r="Y40" s="0" t="inlineStr">
+      <c r="AA40" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -5450,20 +5872,30 @@
       </c>
       <c r="V41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-04-09</t>
         </is>
       </c>
       <c r="W41" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y41" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X41" s="0" t="inlineStr">
+      <c r="Z41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/65kx-0a28</t>
         </is>
       </c>
-      <c r="Y41" s="0" t="inlineStr">
+      <c r="AA41" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -5577,20 +6009,30 @@
       </c>
       <c r="V42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-07-24</t>
         </is>
       </c>
       <c r="W42" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y42" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X42" s="0" t="inlineStr">
+      <c r="Z42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/aess-6m62</t>
         </is>
       </c>
-      <c r="Y42" s="0" t="inlineStr">
+      <c r="AA42" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -5704,20 +6146,30 @@
       </c>
       <c r="V43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="W43" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y43" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X43" s="0" t="inlineStr">
+      <c r="Z43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/b2b3-m644</t>
         </is>
       </c>
-      <c r="Y43" s="0" t="inlineStr">
+      <c r="AA43" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -5831,20 +6283,30 @@
       </c>
       <c r="V44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="W44" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y44" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X44" s="0" t="inlineStr">
+      <c r="Z44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/cckr-7v25</t>
         </is>
       </c>
-      <c r="Y44" s="0" t="inlineStr">
+      <c r="AA44" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -5958,20 +6420,30 @@
       </c>
       <c r="V45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-02-24</t>
         </is>
       </c>
       <c r="W45" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y45" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X45" s="0" t="inlineStr">
+      <c r="Z45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/d7j4-gx12</t>
         </is>
       </c>
-      <c r="Y45" s="0" t="inlineStr">
+      <c r="AA45" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -6085,20 +6557,30 @@
       </c>
       <c r="V46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-08-06</t>
         </is>
       </c>
       <c r="W46" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y46" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X46" s="0" t="inlineStr">
+      <c r="Z46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/emke-w063</t>
         </is>
       </c>
-      <c r="Y46" s="0" t="inlineStr">
+      <c r="AA46" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -6212,20 +6694,30 @@
       </c>
       <c r="V47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-25</t>
         </is>
       </c>
       <c r="W47" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y47" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X47" s="0" t="inlineStr">
+      <c r="Z47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/fcqx-1009</t>
         </is>
       </c>
-      <c r="Y47" s="0" t="inlineStr">
+      <c r="AA47" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -6339,20 +6831,30 @@
       </c>
       <c r="V48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="W48" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y48" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X48" s="0" t="inlineStr">
+      <c r="Z48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/fkzg-kt33</t>
         </is>
       </c>
-      <c r="Y48" s="0" t="inlineStr">
+      <c r="AA48" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -6466,20 +6968,30 @@
       </c>
       <c r="V49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="W49" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y49" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X49" s="0" t="inlineStr">
+      <c r="Z49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/fssj-fe85</t>
         </is>
       </c>
-      <c r="Y49" s="0" t="inlineStr">
+      <c r="AA49" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -6593,20 +7105,30 @@
       </c>
       <c r="V50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-08-19</t>
         </is>
       </c>
       <c r="W50" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y50" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X50" s="0" t="inlineStr">
+      <c r="Z50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/fye2-yk53</t>
         </is>
       </c>
-      <c r="Y50" s="0" t="inlineStr">
+      <c r="AA50" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -6720,20 +7242,30 @@
       </c>
       <c r="V51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-14</t>
         </is>
       </c>
       <c r="W51" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y51" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X51" s="0" t="inlineStr">
+      <c r="Z51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/gy19-2j41</t>
         </is>
       </c>
-      <c r="Y51" s="0" t="inlineStr">
+      <c r="AA51" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -6847,20 +7379,30 @@
       </c>
       <c r="V52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-05-27</t>
         </is>
       </c>
       <c r="W52" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y52" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X52" s="0" t="inlineStr">
+      <c r="Z52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/hq4k-bw52</t>
         </is>
       </c>
-      <c r="Y52" s="0" t="inlineStr">
+      <c r="AA52" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -6974,20 +7516,30 @@
       </c>
       <c r="V53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-07-08</t>
         </is>
       </c>
       <c r="W53" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y53" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X53" s="0" t="inlineStr">
+      <c r="Z53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/jxrb-a760</t>
         </is>
       </c>
-      <c r="Y53" s="0" t="inlineStr">
+      <c r="AA53" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -7101,20 +7653,30 @@
       </c>
       <c r="V54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-03</t>
         </is>
       </c>
       <c r="W54" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y54" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X54" s="0" t="inlineStr">
+      <c r="Z54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/k9kh-y971</t>
         </is>
       </c>
-      <c r="Y54" s="0" t="inlineStr">
+      <c r="AA54" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -7228,20 +7790,30 @@
       </c>
       <c r="V55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-01</t>
         </is>
       </c>
       <c r="W55" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y55" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X55" s="0" t="inlineStr">
+      <c r="Z55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/mpqr-r886</t>
         </is>
       </c>
-      <c r="Y55" s="0" t="inlineStr">
+      <c r="AA55" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -7355,20 +7927,30 @@
       </c>
       <c r="V56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-03-12</t>
         </is>
       </c>
       <c r="W56" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y56" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X56" s="0" t="inlineStr">
+      <c r="Z56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4320204</t>
         </is>
       </c>
-      <c r="Y56" s="0" t="inlineStr">
+      <c r="AA56" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -7482,20 +8064,30 @@
       </c>
       <c r="V57" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-19</t>
+        </is>
+      </c>
+      <c r="W57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X57" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590206</t>
         </is>
       </c>
-      <c r="W57" s="0" t="inlineStr">
+      <c r="Y57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X57" s="0" t="inlineStr">
+      <c r="Z57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590205</t>
         </is>
       </c>
-      <c r="Y57" s="0" t="inlineStr">
+      <c r="AA57" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -7609,20 +8201,30 @@
       </c>
       <c r="V58" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-19</t>
+        </is>
+      </c>
+      <c r="W58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X58" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590205</t>
         </is>
       </c>
-      <c r="W58" s="0" t="inlineStr">
+      <c r="Y58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X58" s="0" t="inlineStr">
+      <c r="Z58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590206</t>
         </is>
       </c>
-      <c r="Y58" s="0" t="inlineStr">
+      <c r="AA58" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -7736,20 +8338,30 @@
       </c>
       <c r="V59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-03-19</t>
         </is>
       </c>
       <c r="W59" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y59" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X59" s="0" t="inlineStr">
+      <c r="Z59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590207</t>
         </is>
       </c>
-      <c r="Y59" s="0" t="inlineStr">
+      <c r="AA59" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -7863,20 +8475,30 @@
       </c>
       <c r="V60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-03-19</t>
         </is>
       </c>
       <c r="W60" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X60" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y60" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X60" s="0" t="inlineStr">
+      <c r="Z60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590208</t>
         </is>
       </c>
-      <c r="Y60" s="0" t="inlineStr">
+      <c r="AA60" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -7990,20 +8612,30 @@
       </c>
       <c r="V61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-03-19</t>
         </is>
       </c>
       <c r="W61" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X61" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y61" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X61" s="0" t="inlineStr">
+      <c r="Z61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590209</t>
         </is>
       </c>
-      <c r="Y61" s="0" t="inlineStr">
+      <c r="AA61" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -8117,20 +8749,30 @@
       </c>
       <c r="V62" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-19</t>
+        </is>
+      </c>
+      <c r="W62" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X62" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590211</t>
         </is>
       </c>
-      <c r="W62" s="0" t="inlineStr">
+      <c r="Y62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X62" s="0" t="inlineStr">
+      <c r="Z62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590210</t>
         </is>
       </c>
-      <c r="Y62" s="0" t="inlineStr">
+      <c r="AA62" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -8244,20 +8886,30 @@
       </c>
       <c r="V63" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-19</t>
+        </is>
+      </c>
+      <c r="W63" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X63" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590210</t>
         </is>
       </c>
-      <c r="W63" s="0" t="inlineStr">
+      <c r="Y63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X63" s="0" t="inlineStr">
+      <c r="Z63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590211</t>
         </is>
       </c>
-      <c r="Y63" s="0" t="inlineStr">
+      <c r="AA63" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -8371,20 +9023,30 @@
       </c>
       <c r="V64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-03-20</t>
         </is>
       </c>
       <c r="W64" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X64" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y64" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X64" s="0" t="inlineStr">
+      <c r="Z64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590212</t>
         </is>
       </c>
-      <c r="Y64" s="0" t="inlineStr">
+      <c r="AA64" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -8498,20 +9160,30 @@
       </c>
       <c r="V65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-03-20</t>
         </is>
       </c>
       <c r="W65" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X65" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y65" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X65" s="0" t="inlineStr">
+      <c r="Z65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590213</t>
         </is>
       </c>
-      <c r="Y65" s="0" t="inlineStr">
+      <c r="AA65" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -8625,20 +9297,30 @@
       </c>
       <c r="V66" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-20</t>
+        </is>
+      </c>
+      <c r="W66" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X66" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: 10.25923/na21oar4590214</t>
         </is>
       </c>
-      <c r="W66" s="0" t="inlineStr">
+      <c r="Y66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X66" s="0" t="inlineStr">
+      <c r="Z66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590214</t>
         </is>
       </c>
-      <c r="Y66" s="0" t="inlineStr">
+      <c r="AA66" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -8752,20 +9434,30 @@
       </c>
       <c r="V67" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-20</t>
+        </is>
+      </c>
+      <c r="W67" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X67" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590214</t>
         </is>
       </c>
-      <c r="W67" s="0" t="inlineStr">
+      <c r="Y67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X67" s="0" t="inlineStr">
+      <c r="Z67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590215</t>
         </is>
       </c>
-      <c r="Y67" s="0" t="inlineStr">
+      <c r="AA67" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -8879,20 +9571,30 @@
       </c>
       <c r="V68" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-20</t>
+        </is>
+      </c>
+      <c r="W68" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X68" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590217</t>
         </is>
       </c>
-      <c r="W68" s="0" t="inlineStr">
+      <c r="Y68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X68" s="0" t="inlineStr">
+      <c r="Z68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590216</t>
         </is>
       </c>
-      <c r="Y68" s="0" t="inlineStr">
+      <c r="AA68" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -9006,20 +9708,30 @@
       </c>
       <c r="V69" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-20</t>
+        </is>
+      </c>
+      <c r="W69" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X69" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590216</t>
         </is>
       </c>
-      <c r="W69" s="0" t="inlineStr">
+      <c r="Y69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X69" s="0" t="inlineStr">
+      <c r="Z69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590217</t>
         </is>
       </c>
-      <c r="Y69" s="0" t="inlineStr">
+      <c r="AA69" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -9133,20 +9845,30 @@
       </c>
       <c r="V70" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-20</t>
+        </is>
+      </c>
+      <c r="W70" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X70" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590219</t>
         </is>
       </c>
-      <c r="W70" s="0" t="inlineStr">
+      <c r="Y70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X70" s="0" t="inlineStr">
+      <c r="Z70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590218</t>
         </is>
       </c>
-      <c r="Y70" s="0" t="inlineStr">
+      <c r="AA70" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -9260,20 +9982,30 @@
       </c>
       <c r="V71" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-20</t>
+        </is>
+      </c>
+      <c r="W71" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X71" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: http://doi.org/10.25923/na21oar4590218</t>
         </is>
       </c>
-      <c r="W71" s="0" t="inlineStr">
+      <c r="Y71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X71" s="0" t="inlineStr">
+      <c r="Z71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na21oar4590219</t>
         </is>
       </c>
-      <c r="Y71" s="0" t="inlineStr">
+      <c r="AA71" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -9387,20 +10119,30 @@
       </c>
       <c r="V72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W72" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X72" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y72" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X72" s="0" t="inlineStr">
+      <c r="Z72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4050416</t>
         </is>
       </c>
-      <c r="Y72" s="0" t="inlineStr">
+      <c r="AA72" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -9514,20 +10256,30 @@
       </c>
       <c r="V73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W73" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y73" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X73" s="0" t="inlineStr">
+      <c r="Z73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4050503i</t>
         </is>
       </c>
-      <c r="Y73" s="0" t="inlineStr">
+      <c r="AA73" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -9641,20 +10393,30 @@
       </c>
       <c r="V74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W74" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X74" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y74" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X74" s="0" t="inlineStr">
+      <c r="Z74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590359</t>
         </is>
       </c>
-      <c r="Y74" s="0" t="inlineStr">
+      <c r="AA74" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -9768,20 +10530,30 @@
       </c>
       <c r="V75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W75" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X75" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y75" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X75" s="0" t="inlineStr">
+      <c r="Z75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590360</t>
         </is>
       </c>
-      <c r="Y75" s="0" t="inlineStr">
+      <c r="AA75" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -9895,20 +10667,30 @@
       </c>
       <c r="V76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W76" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X76" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y76" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X76" s="0" t="inlineStr">
+      <c r="Z76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590361</t>
         </is>
       </c>
-      <c r="Y76" s="0" t="inlineStr">
+      <c r="AA76" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -10022,20 +10804,30 @@
       </c>
       <c r="V77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W77" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X77" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y77" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X77" s="0" t="inlineStr">
+      <c r="Z77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590362</t>
         </is>
       </c>
-      <c r="Y77" s="0" t="inlineStr">
+      <c r="AA77" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -10149,20 +10941,30 @@
       </c>
       <c r="V78" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-02-21</t>
+        </is>
+      </c>
+      <c r="W78" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X78" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: https://doi.org/NA23OAR4590364</t>
         </is>
       </c>
-      <c r="W78" s="0" t="inlineStr">
+      <c r="Y78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X78" s="0" t="inlineStr">
+      <c r="Z78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590363</t>
         </is>
       </c>
-      <c r="Y78" s="0" t="inlineStr">
+      <c r="AA78" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -10276,20 +11078,30 @@
       </c>
       <c r="V79" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-02-21</t>
+        </is>
+      </c>
+      <c r="W79" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X79" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsPartOf: https://doi.org/10.25923/na23oar4590363</t>
         </is>
       </c>
-      <c r="W79" s="0" t="inlineStr">
+      <c r="Y79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X79" s="0" t="inlineStr">
+      <c r="Z79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590364</t>
         </is>
       </c>
-      <c r="Y79" s="0" t="inlineStr">
+      <c r="AA79" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -10403,20 +11215,30 @@
       </c>
       <c r="V80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W80" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X80" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y80" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X80" s="0" t="inlineStr">
+      <c r="Z80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590366</t>
         </is>
       </c>
-      <c r="Y80" s="0" t="inlineStr">
+      <c r="AA80" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -10530,20 +11352,30 @@
       </c>
       <c r="V81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W81" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X81" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y81" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X81" s="0" t="inlineStr">
+      <c r="Z81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590367</t>
         </is>
       </c>
-      <c r="Y81" s="0" t="inlineStr">
+      <c r="AA81" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -10657,20 +11489,30 @@
       </c>
       <c r="V82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W82" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X82" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y82" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X82" s="0" t="inlineStr">
+      <c r="Z82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590368</t>
         </is>
       </c>
-      <c r="Y82" s="0" t="inlineStr">
+      <c r="AA82" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -10784,20 +11626,30 @@
       </c>
       <c r="V83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W83" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X83" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y83" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X83" s="0" t="inlineStr">
+      <c r="Z83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/na23oar4590369</t>
         </is>
       </c>
-      <c r="Y83" s="0" t="inlineStr">
+      <c r="AA83" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -10911,20 +11763,30 @@
       </c>
       <c r="V84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-16</t>
         </is>
       </c>
       <c r="W84" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X84" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y84" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X84" s="0" t="inlineStr">
+      <c r="Z84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/nkn2-vt59</t>
         </is>
       </c>
-      <c r="Y84" s="0" t="inlineStr">
+      <c r="AA84" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -11038,20 +11900,30 @@
       </c>
       <c r="V85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-08-01</t>
         </is>
       </c>
       <c r="W85" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X85" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y85" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X85" s="0" t="inlineStr">
+      <c r="Z85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/nm97-m303</t>
         </is>
       </c>
-      <c r="Y85" s="0" t="inlineStr">
+      <c r="AA85" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -11165,20 +12037,30 @@
       </c>
       <c r="V86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-02-21</t>
         </is>
       </c>
       <c r="W86" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X86" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y86" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X86" s="0" t="inlineStr">
+      <c r="Z86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/t7t6-m677</t>
         </is>
       </c>
-      <c r="Y86" s="0" t="inlineStr">
+      <c r="AA86" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -11292,20 +12174,30 @@
       </c>
       <c r="V87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-04</t>
         </is>
       </c>
       <c r="W87" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X87" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y87" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X87" s="0" t="inlineStr">
+      <c r="Z87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/xtmp-8529</t>
         </is>
       </c>
-      <c r="Y87" s="0" t="inlineStr">
+      <c r="AA87" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -11419,20 +12311,30 @@
       </c>
       <c r="V88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="W88" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X88" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y88" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X88" s="0" t="inlineStr">
+      <c r="Z88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/y7ft-hn02</t>
         </is>
       </c>
-      <c r="Y88" s="0" t="inlineStr">
+      <c r="AA88" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -11546,20 +12448,30 @@
       </c>
       <c r="V89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-02-03</t>
         </is>
       </c>
       <c r="W89" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X89" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y89" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X89" s="0" t="inlineStr">
+      <c r="Z89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.25923/z3r8-z649</t>
         </is>
       </c>
-      <c r="Y89" s="0" t="inlineStr">
+      <c r="AA89" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -11673,20 +12585,30 @@
       </c>
       <c r="V90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-31</t>
         </is>
       </c>
       <c r="W90" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X90" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y90" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X90" s="0" t="inlineStr">
+      <c r="Z90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.3886/e109964</t>
         </is>
       </c>
-      <c r="Y90" s="0" t="inlineStr">
+      <c r="AA90" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -11800,20 +12722,30 @@
       </c>
       <c r="V91" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-29</t>
         </is>
       </c>
       <c r="W91" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X91" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y91" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X91" s="0" t="inlineStr">
+      <c r="Z91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.3886/e109964v1</t>
         </is>
       </c>
-      <c r="Y91" s="0" t="inlineStr">
+      <c r="AA91" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -11927,20 +12859,30 @@
       </c>
       <c r="V92" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2023-10-03</t>
+        </is>
+      </c>
+      <c r="W92" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X92" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.3886/e109964</t>
         </is>
       </c>
-      <c r="W92" s="0" t="inlineStr">
+      <c r="Y92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X92" s="0" t="inlineStr">
+      <c r="Z92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.3886/e109964v1-142043</t>
         </is>
       </c>
-      <c r="Y92" s="0" t="inlineStr">
+      <c r="AA92" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -12054,20 +12996,30 @@
       </c>
       <c r="V93" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="W93" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X93" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y93" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X93" s="0" t="inlineStr">
+      <c r="Z93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.4211/hs.3c3a2f3d491c4e4aa4ccb6764806eb8a</t>
         </is>
       </c>
-      <c r="Y93" s="0" t="inlineStr">
+      <c r="AA93" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -12181,20 +13133,30 @@
       </c>
       <c r="V94" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="W94" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X94" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y94" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X94" s="0" t="inlineStr">
+      <c r="Z94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.4211/hs.9460830270ec4d8b9d9c4260cca2114d</t>
         </is>
       </c>
-      <c r="Y94" s="0" t="inlineStr">
+      <c r="AA94" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -12283,7 +13245,7 @@
       </c>
       <c r="Q95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R95" s="0" t="inlineStr">
@@ -12308,20 +13270,30 @@
       </c>
       <c r="V95" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-06-24</t>
         </is>
       </c>
       <c r="W95" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X95" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y95" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X95" s="0" t="inlineStr">
+      <c r="Z95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.05qfttf5h</t>
         </is>
       </c>
-      <c r="Y95" s="0" t="inlineStr">
+      <c r="AA95" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -12410,7 +13382,7 @@
       </c>
       <c r="Q96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R96" s="0" t="inlineStr">
@@ -12435,20 +13407,30 @@
       </c>
       <c r="V96" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-08-21</t>
         </is>
       </c>
       <c r="W96" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X96" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y96" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X96" s="0" t="inlineStr">
+      <c r="Z96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.0gb5mkm6t</t>
         </is>
       </c>
-      <c r="Y96" s="0" t="inlineStr">
+      <c r="AA96" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -12537,7 +13519,7 @@
       </c>
       <c r="Q97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R97" s="0" t="inlineStr">
@@ -12562,20 +13544,30 @@
       </c>
       <c r="V97" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-03-11</t>
         </is>
       </c>
       <c r="W97" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X97" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y97" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X97" s="0" t="inlineStr">
+      <c r="Z97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.0gb5mkmbc</t>
         </is>
       </c>
-      <c r="Y97" s="0" t="inlineStr">
+      <c r="AA97" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -12664,7 +13656,7 @@
       </c>
       <c r="Q98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R98" s="0" t="inlineStr">
@@ -12689,20 +13681,30 @@
       </c>
       <c r="V98" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="W98" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X98" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y98" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X98" s="0" t="inlineStr">
+      <c r="Z98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.0rxwdbs7w</t>
         </is>
       </c>
-      <c r="Y98" s="0" t="inlineStr">
+      <c r="AA98" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -12791,7 +13793,7 @@
       </c>
       <c r="Q99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R99" s="0" t="inlineStr">
@@ -12816,20 +13818,30 @@
       </c>
       <c r="V99" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-10-11</t>
         </is>
       </c>
       <c r="W99" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X99" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y99" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X99" s="0" t="inlineStr">
+      <c r="Z99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.2bvq83br4</t>
         </is>
       </c>
-      <c r="Y99" s="0" t="inlineStr">
+      <c r="AA99" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -12918,7 +13930,7 @@
       </c>
       <c r="Q100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R100" s="0" t="inlineStr">
@@ -12943,20 +13955,30 @@
       </c>
       <c r="V100" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-04-04</t>
         </is>
       </c>
       <c r="W100" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y100" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X100" s="0" t="inlineStr">
+      <c r="Z100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.2jm63xstt</t>
         </is>
       </c>
-      <c r="Y100" s="0" t="inlineStr">
+      <c r="AA100" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -13045,7 +14067,7 @@
       </c>
       <c r="Q101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R101" s="0" t="inlineStr">
@@ -13070,20 +14092,30 @@
       </c>
       <c r="V101" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-11-25</t>
         </is>
       </c>
       <c r="W101" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y101" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X101" s="0" t="inlineStr">
+      <c r="Z101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.2z34tmpzp</t>
         </is>
       </c>
-      <c r="Y101" s="0" t="inlineStr">
+      <c r="AA101" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part001.csv</t>
         </is>
@@ -13172,7 +14204,7 @@
       </c>
       <c r="Q102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R102" s="0" t="inlineStr">
@@ -13197,20 +14229,30 @@
       </c>
       <c r="V102" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-10-19</t>
         </is>
       </c>
       <c r="W102" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y102" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X102" s="0" t="inlineStr">
+      <c r="Z102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.3n5tb2rq4</t>
         </is>
       </c>
-      <c r="Y102" s="0" t="inlineStr">
+      <c r="AA102" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -13299,7 +14341,7 @@
       </c>
       <c r="Q103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R103" s="0" t="inlineStr">
@@ -13324,20 +14366,30 @@
       </c>
       <c r="V103" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-02-19</t>
         </is>
       </c>
       <c r="W103" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y103" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X103" s="0" t="inlineStr">
+      <c r="Z103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.4qrfj6qhj</t>
         </is>
       </c>
-      <c r="Y103" s="0" t="inlineStr">
+      <c r="AA103" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -13426,7 +14478,7 @@
       </c>
       <c r="Q104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R104" s="0" t="inlineStr">
@@ -13451,20 +14503,30 @@
       </c>
       <c r="V104" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-10-18</t>
         </is>
       </c>
       <c r="W104" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y104" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X104" s="0" t="inlineStr">
+      <c r="Z104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.63xsj3v88</t>
         </is>
       </c>
-      <c r="Y104" s="0" t="inlineStr">
+      <c r="AA104" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -13553,7 +14615,7 @@
       </c>
       <c r="Q105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R105" s="0" t="inlineStr">
@@ -13578,20 +14640,30 @@
       </c>
       <c r="V105" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-10-03</t>
         </is>
       </c>
       <c r="W105" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y105" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X105" s="0" t="inlineStr">
+      <c r="Z105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.7pvmcvf39</t>
         </is>
       </c>
-      <c r="Y105" s="0" t="inlineStr">
+      <c r="AA105" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -13680,7 +14752,7 @@
       </c>
       <c r="Q106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R106" s="0" t="inlineStr">
@@ -13705,20 +14777,30 @@
       </c>
       <c r="V106" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-04-15</t>
         </is>
       </c>
       <c r="W106" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y106" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X106" s="0" t="inlineStr">
+      <c r="Z106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.8pk0p2npb</t>
         </is>
       </c>
-      <c r="Y106" s="0" t="inlineStr">
+      <c r="AA106" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -13807,7 +14889,7 @@
       </c>
       <c r="Q107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R107" s="0" t="inlineStr">
@@ -13832,20 +14914,30 @@
       </c>
       <c r="V107" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-02-07</t>
         </is>
       </c>
       <c r="W107" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y107" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X107" s="0" t="inlineStr">
+      <c r="Z107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.b2rbnzsp5</t>
         </is>
       </c>
-      <c r="Y107" s="0" t="inlineStr">
+      <c r="AA107" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -13934,7 +15026,7 @@
       </c>
       <c r="Q108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R108" s="0" t="inlineStr">
@@ -13959,20 +15051,30 @@
       </c>
       <c r="V108" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-04-24</t>
         </is>
       </c>
       <c r="W108" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y108" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X108" s="0" t="inlineStr">
+      <c r="Z108" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.b5mkkwhh9</t>
         </is>
       </c>
-      <c r="Y108" s="0" t="inlineStr">
+      <c r="AA108" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -14061,7 +15163,7 @@
       </c>
       <c r="Q109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R109" s="0" t="inlineStr">
@@ -14086,20 +15188,30 @@
       </c>
       <c r="V109" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-01-02</t>
         </is>
       </c>
       <c r="W109" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y109" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X109" s="0" t="inlineStr">
+      <c r="Z109" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.c2fqz61cv</t>
         </is>
       </c>
-      <c r="Y109" s="0" t="inlineStr">
+      <c r="AA109" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -14188,7 +15300,7 @@
       </c>
       <c r="Q110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R110" s="0" t="inlineStr">
@@ -14213,20 +15325,30 @@
       </c>
       <c r="V110" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-03</t>
         </is>
       </c>
       <c r="W110" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y110" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X110" s="0" t="inlineStr">
+      <c r="Z110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.f4qrfj71p</t>
         </is>
       </c>
-      <c r="Y110" s="0" t="inlineStr">
+      <c r="AA110" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -14315,7 +15437,7 @@
       </c>
       <c r="Q111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R111" s="0" t="inlineStr">
@@ -14340,20 +15462,30 @@
       </c>
       <c r="V111" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
       <c r="W111" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y111" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X111" s="0" t="inlineStr">
+      <c r="Z111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.gf1vhhmw0</t>
         </is>
       </c>
-      <c r="Y111" s="0" t="inlineStr">
+      <c r="AA111" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -14442,7 +15574,7 @@
       </c>
       <c r="Q112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R112" s="0" t="inlineStr">
@@ -14467,20 +15599,30 @@
       </c>
       <c r="V112" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-09-20</t>
         </is>
       </c>
       <c r="W112" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y112" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X112" s="0" t="inlineStr">
+      <c r="Z112" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.gtht76hsk</t>
         </is>
       </c>
-      <c r="Y112" s="0" t="inlineStr">
+      <c r="AA112" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -14569,7 +15711,7 @@
       </c>
       <c r="Q113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R113" s="0" t="inlineStr">
@@ -14594,20 +15736,30 @@
       </c>
       <c r="V113" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-11-30</t>
         </is>
       </c>
       <c r="W113" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y113" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X113" s="0" t="inlineStr">
+      <c r="Z113" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.gxd2547rt</t>
         </is>
       </c>
-      <c r="Y113" s="0" t="inlineStr">
+      <c r="AA113" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -14696,7 +15848,7 @@
       </c>
       <c r="Q114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R114" s="0" t="inlineStr">
@@ -14721,20 +15873,30 @@
       </c>
       <c r="V114" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-10-31</t>
         </is>
       </c>
       <c r="W114" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y114" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X114" s="0" t="inlineStr">
+      <c r="Z114" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.h70rxwdqn</t>
         </is>
       </c>
-      <c r="Y114" s="0" t="inlineStr">
+      <c r="AA114" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -14823,7 +15985,7 @@
       </c>
       <c r="Q115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R115" s="0" t="inlineStr">
@@ -14848,20 +16010,30 @@
       </c>
       <c r="V115" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-04-04</t>
         </is>
       </c>
       <c r="W115" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y115" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X115" s="0" t="inlineStr">
+      <c r="Z115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.h9w0vt4nq</t>
         </is>
       </c>
-      <c r="Y115" s="0" t="inlineStr">
+      <c r="AA115" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -14950,7 +16122,7 @@
       </c>
       <c r="Q116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R116" s="0" t="inlineStr">
@@ -14975,20 +16147,30 @@
       </c>
       <c r="V116" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-10-07</t>
         </is>
       </c>
       <c r="W116" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y116" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X116" s="0" t="inlineStr">
+      <c r="Z116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.kwh70rzdx</t>
         </is>
       </c>
-      <c r="Y116" s="0" t="inlineStr">
+      <c r="AA116" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -15077,7 +16259,7 @@
       </c>
       <c r="Q117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R117" s="0" t="inlineStr">
@@ -15102,20 +16284,30 @@
       </c>
       <c r="V117" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-07-20</t>
         </is>
       </c>
       <c r="W117" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y117" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X117" s="0" t="inlineStr">
+      <c r="Z117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.kwh70rzfc</t>
         </is>
       </c>
-      <c r="Y117" s="0" t="inlineStr">
+      <c r="AA117" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -15204,7 +16396,7 @@
       </c>
       <c r="Q118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R118" s="0" t="inlineStr">
@@ -15229,20 +16421,30 @@
       </c>
       <c r="V118" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-04-21</t>
         </is>
       </c>
       <c r="W118" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y118" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X118" s="0" t="inlineStr">
+      <c r="Z118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.m905qfv60</t>
         </is>
       </c>
-      <c r="Y118" s="0" t="inlineStr">
+      <c r="AA118" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -15331,7 +16533,7 @@
       </c>
       <c r="Q119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R119" s="0" t="inlineStr">
@@ -15356,20 +16558,30 @@
       </c>
       <c r="V119" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-08-09</t>
         </is>
       </c>
       <c r="W119" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y119" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X119" s="0" t="inlineStr">
+      <c r="Z119" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.rbnzs7hq0</t>
         </is>
       </c>
-      <c r="Y119" s="0" t="inlineStr">
+      <c r="AA119" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -15458,7 +16670,7 @@
       </c>
       <c r="Q120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R120" s="0" t="inlineStr">
@@ -15483,20 +16695,30 @@
       </c>
       <c r="V120" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2022-12-17</t>
         </is>
       </c>
       <c r="W120" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y120" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X120" s="0" t="inlineStr">
+      <c r="Z120" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.v15dv4209</t>
         </is>
       </c>
-      <c r="Y120" s="0" t="inlineStr">
+      <c r="AA120" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -15585,7 +16807,7 @@
       </c>
       <c r="Q121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R121" s="0" t="inlineStr">
@@ -15610,20 +16832,30 @@
       </c>
       <c r="V121" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-01-09</t>
         </is>
       </c>
       <c r="W121" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y121" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X121" s="0" t="inlineStr">
+      <c r="Z121" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.v41ns1s4v</t>
         </is>
       </c>
-      <c r="Y121" s="0" t="inlineStr">
+      <c r="AA121" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -15712,7 +16944,7 @@
       </c>
       <c r="Q122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="R122" s="0" t="inlineStr">
@@ -15737,20 +16969,30 @@
       </c>
       <c r="V122" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-04-04</t>
         </is>
       </c>
       <c r="W122" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y122" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X122" s="0" t="inlineStr">
+      <c r="Z122" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5061/dryad.zs7h44jf2</t>
         </is>
       </c>
-      <c r="Y122" s="0" t="inlineStr">
+      <c r="AA122" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -15864,20 +17106,30 @@
       </c>
       <c r="V123" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-06-12</t>
+        </is>
+      </c>
+      <c r="W123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X123" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.11623054</t>
         </is>
       </c>
-      <c r="W123" s="0" t="inlineStr">
+      <c r="Y123" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X123" s="0" t="inlineStr">
+      <c r="Z123" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.11623053</t>
         </is>
       </c>
-      <c r="Y123" s="0" t="inlineStr">
+      <c r="AA123" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -15991,20 +17243,30 @@
       </c>
       <c r="V124" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-06-12</t>
+        </is>
+      </c>
+      <c r="W124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X124" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.11623053</t>
         </is>
       </c>
-      <c r="W124" s="0" t="inlineStr">
+      <c r="Y124" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X124" s="0" t="inlineStr">
+      <c r="Z124" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.11623054</t>
         </is>
       </c>
-      <c r="Y124" s="0" t="inlineStr">
+      <c r="AA124" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -16118,20 +17380,30 @@
       </c>
       <c r="V125" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-06-26</t>
+        </is>
+      </c>
+      <c r="W125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X125" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.12557547; HasVersion: 10.5281/zenodo.12560629; HasVersion: 10.5281/zenodo.12557521; HasVersion: 10.5281/zenodo.12625308; HasVersion: 10.5281/zenodo.12557265; HasVersion: 10.5281/zenodo.12560367; HasVersion: 10.5281/zenodo.12638402</t>
         </is>
       </c>
-      <c r="W125" s="0" t="inlineStr">
+      <c r="Y125" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X125" s="0" t="inlineStr">
+      <c r="Z125" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.12557264</t>
         </is>
       </c>
-      <c r="Y125" s="0" t="inlineStr">
+      <c r="AA125" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -16245,20 +17517,30 @@
       </c>
       <c r="V126" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-06-26</t>
+        </is>
+      </c>
+      <c r="W126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X126" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.12557264</t>
         </is>
       </c>
-      <c r="W126" s="0" t="inlineStr">
+      <c r="Y126" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X126" s="0" t="inlineStr">
+      <c r="Z126" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.12557265</t>
         </is>
       </c>
-      <c r="Y126" s="0" t="inlineStr">
+      <c r="AA126" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -16372,20 +17654,30 @@
       </c>
       <c r="V127" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-06-26</t>
+        </is>
+      </c>
+      <c r="W127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X127" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.12557264</t>
         </is>
       </c>
-      <c r="W127" s="0" t="inlineStr">
+      <c r="Y127" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X127" s="0" t="inlineStr">
+      <c r="Z127" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.12557521</t>
         </is>
       </c>
-      <c r="Y127" s="0" t="inlineStr">
+      <c r="AA127" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -16499,20 +17791,30 @@
       </c>
       <c r="V128" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-06-26</t>
+        </is>
+      </c>
+      <c r="W128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X128" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.12557264</t>
         </is>
       </c>
-      <c r="W128" s="0" t="inlineStr">
+      <c r="Y128" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X128" s="0" t="inlineStr">
+      <c r="Z128" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.12557547</t>
         </is>
       </c>
-      <c r="Y128" s="0" t="inlineStr">
+      <c r="AA128" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -16626,20 +17928,30 @@
       </c>
       <c r="V129" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-06-27</t>
+        </is>
+      </c>
+      <c r="W129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X129" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.12557264</t>
         </is>
       </c>
-      <c r="W129" s="0" t="inlineStr">
+      <c r="Y129" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X129" s="0" t="inlineStr">
+      <c r="Z129" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.12560367</t>
         </is>
       </c>
-      <c r="Y129" s="0" t="inlineStr">
+      <c r="AA129" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -16753,20 +18065,30 @@
       </c>
       <c r="V130" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-06-27</t>
+        </is>
+      </c>
+      <c r="W130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X130" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.12557264</t>
         </is>
       </c>
-      <c r="W130" s="0" t="inlineStr">
+      <c r="Y130" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X130" s="0" t="inlineStr">
+      <c r="Z130" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.12560629</t>
         </is>
       </c>
-      <c r="Y130" s="0" t="inlineStr">
+      <c r="AA130" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -16880,20 +18202,30 @@
       </c>
       <c r="V131" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-07-02</t>
+        </is>
+      </c>
+      <c r="W131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X131" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.12557264</t>
         </is>
       </c>
-      <c r="W131" s="0" t="inlineStr">
+      <c r="Y131" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X131" s="0" t="inlineStr">
+      <c r="Z131" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.12625308</t>
         </is>
       </c>
-      <c r="Y131" s="0" t="inlineStr">
+      <c r="AA131" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -17007,20 +18339,30 @@
       </c>
       <c r="V132" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-07-04</t>
+        </is>
+      </c>
+      <c r="W132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X132" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.12557264</t>
         </is>
       </c>
-      <c r="W132" s="0" t="inlineStr">
+      <c r="Y132" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X132" s="0" t="inlineStr">
+      <c r="Z132" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.12638402</t>
         </is>
       </c>
-      <c r="Y132" s="0" t="inlineStr">
+      <c r="AA132" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -17134,20 +18476,30 @@
       </c>
       <c r="V133" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-10-18</t>
+        </is>
+      </c>
+      <c r="W133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X133" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.13625365; IsPartOf: 1878-1470</t>
         </is>
       </c>
-      <c r="W133" s="0" t="inlineStr">
+      <c r="Y133" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X133" s="0" t="inlineStr">
+      <c r="Z133" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.13625364</t>
         </is>
       </c>
-      <c r="Y133" s="0" t="inlineStr">
+      <c r="AA133" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -17261,20 +18613,30 @@
       </c>
       <c r="V134" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2024-10-18</t>
+        </is>
+      </c>
+      <c r="W134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X134" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.13625364; IsPartOf: 1878-1470</t>
         </is>
       </c>
-      <c r="W134" s="0" t="inlineStr">
+      <c r="Y134" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X134" s="0" t="inlineStr">
+      <c r="Z134" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.13625365</t>
         </is>
       </c>
-      <c r="Y134" s="0" t="inlineStr">
+      <c r="AA134" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -17388,20 +18750,30 @@
       </c>
       <c r="V135" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-12</t>
+        </is>
+      </c>
+      <c r="W135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X135" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.15002615</t>
         </is>
       </c>
-      <c r="W135" s="0" t="inlineStr">
+      <c r="Y135" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X135" s="0" t="inlineStr">
+      <c r="Z135" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15002614</t>
         </is>
       </c>
-      <c r="Y135" s="0" t="inlineStr">
+      <c r="AA135" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -17515,20 +18887,30 @@
       </c>
       <c r="V136" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-03-12</t>
+        </is>
+      </c>
+      <c r="W136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X136" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.15002614</t>
         </is>
       </c>
-      <c r="W136" s="0" t="inlineStr">
+      <c r="Y136" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X136" s="0" t="inlineStr">
+      <c r="Z136" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15002615</t>
         </is>
       </c>
-      <c r="Y136" s="0" t="inlineStr">
+      <c r="AA136" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -17642,20 +19024,30 @@
       </c>
       <c r="V137" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="W137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X137" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.15238132</t>
         </is>
       </c>
-      <c r="W137" s="0" t="inlineStr">
+      <c r="Y137" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X137" s="0" t="inlineStr">
+      <c r="Z137" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15238131</t>
         </is>
       </c>
-      <c r="Y137" s="0" t="inlineStr">
+      <c r="AA137" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -17769,20 +19161,30 @@
       </c>
       <c r="V138" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="W138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X138" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.15238131</t>
         </is>
       </c>
-      <c r="W138" s="0" t="inlineStr">
+      <c r="Y138" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X138" s="0" t="inlineStr">
+      <c r="Z138" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15238132</t>
         </is>
       </c>
-      <c r="Y138" s="0" t="inlineStr">
+      <c r="AA138" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -17896,20 +19298,30 @@
       </c>
       <c r="V139" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-08-29</t>
+        </is>
+      </c>
+      <c r="W139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X139" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.15352579; HasVersion: 10.5281/zenodo.17675895</t>
         </is>
       </c>
-      <c r="W139" s="0" t="inlineStr">
+      <c r="Y139" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X139" s="0" t="inlineStr">
+      <c r="Z139" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15352578</t>
         </is>
       </c>
-      <c r="Y139" s="0" t="inlineStr">
+      <c r="AA139" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -18023,20 +19435,30 @@
       </c>
       <c r="V140" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-08-29</t>
+        </is>
+      </c>
+      <c r="W140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X140" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.15352578</t>
         </is>
       </c>
-      <c r="W140" s="0" t="inlineStr">
+      <c r="Y140" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X140" s="0" t="inlineStr">
+      <c r="Z140" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15352579</t>
         </is>
       </c>
-      <c r="Y140" s="0" t="inlineStr">
+      <c r="AA140" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -18150,20 +19572,30 @@
       </c>
       <c r="V141" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-05-28</t>
+        </is>
+      </c>
+      <c r="W141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X141" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.15538548</t>
         </is>
       </c>
-      <c r="W141" s="0" t="inlineStr">
+      <c r="Y141" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X141" s="0" t="inlineStr">
+      <c r="Z141" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15538547</t>
         </is>
       </c>
-      <c r="Y141" s="0" t="inlineStr">
+      <c r="AA141" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -18277,20 +19709,30 @@
       </c>
       <c r="V142" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-05-28</t>
+        </is>
+      </c>
+      <c r="W142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X142" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.15538547</t>
         </is>
       </c>
-      <c r="W142" s="0" t="inlineStr">
+      <c r="Y142" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X142" s="0" t="inlineStr">
+      <c r="Z142" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15538548</t>
         </is>
       </c>
-      <c r="Y142" s="0" t="inlineStr">
+      <c r="AA142" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -18404,20 +19846,30 @@
       </c>
       <c r="V143" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-06-18</t>
+        </is>
+      </c>
+      <c r="W143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X143" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.15691878</t>
         </is>
       </c>
-      <c r="W143" s="0" t="inlineStr">
+      <c r="Y143" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X143" s="0" t="inlineStr">
+      <c r="Z143" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15691877</t>
         </is>
       </c>
-      <c r="Y143" s="0" t="inlineStr">
+      <c r="AA143" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -18531,20 +19983,30 @@
       </c>
       <c r="V144" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-06-18</t>
+        </is>
+      </c>
+      <c r="W144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X144" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.15691877</t>
         </is>
       </c>
-      <c r="W144" s="0" t="inlineStr">
+      <c r="Y144" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X144" s="0" t="inlineStr">
+      <c r="Z144" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.15691878</t>
         </is>
       </c>
-      <c r="Y144" s="0" t="inlineStr">
+      <c r="AA144" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -18658,20 +20120,30 @@
       </c>
       <c r="V145" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-08-12</t>
+        </is>
+      </c>
+      <c r="W145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X145" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.16583938</t>
         </is>
       </c>
-      <c r="W145" s="0" t="inlineStr">
+      <c r="Y145" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X145" s="0" t="inlineStr">
+      <c r="Z145" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.16583937</t>
         </is>
       </c>
-      <c r="Y145" s="0" t="inlineStr">
+      <c r="AA145" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -18785,20 +20257,30 @@
       </c>
       <c r="V146" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-08-12</t>
+        </is>
+      </c>
+      <c r="W146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X146" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.16583937</t>
         </is>
       </c>
-      <c r="W146" s="0" t="inlineStr">
+      <c r="Y146" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X146" s="0" t="inlineStr">
+      <c r="Z146" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.16583938</t>
         </is>
       </c>
-      <c r="Y146" s="0" t="inlineStr">
+      <c r="AA146" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -18912,20 +20394,30 @@
       </c>
       <c r="V147" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2025-11-21</t>
+        </is>
+      </c>
+      <c r="W147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X147" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.15352578</t>
         </is>
       </c>
-      <c r="W147" s="0" t="inlineStr">
+      <c r="Y147" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X147" s="0" t="inlineStr">
+      <c r="Z147" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.17675895</t>
         </is>
       </c>
-      <c r="Y147" s="0" t="inlineStr">
+      <c r="AA147" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -19039,20 +20531,30 @@
       </c>
       <c r="V148" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-01-29</t>
+        </is>
+      </c>
+      <c r="W148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X148" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.18423546; HasVersion: 10.5281/zenodo.18408783</t>
         </is>
       </c>
-      <c r="W148" s="0" t="inlineStr">
+      <c r="Y148" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X148" s="0" t="inlineStr">
+      <c r="Z148" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.18408782</t>
         </is>
       </c>
-      <c r="Y148" s="0" t="inlineStr">
+      <c r="AA148" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -19166,20 +20668,30 @@
       </c>
       <c r="V149" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
+      <c r="W149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X149" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.18408782</t>
         </is>
       </c>
-      <c r="W149" s="0" t="inlineStr">
+      <c r="Y149" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X149" s="0" t="inlineStr">
+      <c r="Z149" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.18423546</t>
         </is>
       </c>
-      <c r="Y149" s="0" t="inlineStr">
+      <c r="AA149" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -19293,20 +20805,30 @@
       </c>
       <c r="V150" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-06-18</t>
+        </is>
+      </c>
+      <c r="W150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X150" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.18842183</t>
         </is>
       </c>
-      <c r="W150" s="0" t="inlineStr">
+      <c r="Y150" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X150" s="0" t="inlineStr">
+      <c r="Z150" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.18842182</t>
         </is>
       </c>
-      <c r="Y150" s="0" t="inlineStr">
+      <c r="AA150" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -19420,20 +20942,30 @@
       </c>
       <c r="V151" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-06-18</t>
+        </is>
+      </c>
+      <c r="W151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X151" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.18842182</t>
         </is>
       </c>
-      <c r="W151" s="0" t="inlineStr">
+      <c r="Y151" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X151" s="0" t="inlineStr">
+      <c r="Z151" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.18842183</t>
         </is>
       </c>
-      <c r="Y151" s="0" t="inlineStr">
+      <c r="AA151" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -19547,20 +21079,30 @@
       </c>
       <c r="V152" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-04-17</t>
+        </is>
+      </c>
+      <c r="W152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X152" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.19444633</t>
         </is>
       </c>
-      <c r="W152" s="0" t="inlineStr">
+      <c r="Y152" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X152" s="0" t="inlineStr">
+      <c r="Z152" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.19444632</t>
         </is>
       </c>
-      <c r="Y152" s="0" t="inlineStr">
+      <c r="AA152" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -19674,20 +21216,30 @@
       </c>
       <c r="V153" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-04-17</t>
+        </is>
+      </c>
+      <c r="W153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X153" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.19444632</t>
         </is>
       </c>
-      <c r="W153" s="0" t="inlineStr">
+      <c r="Y153" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X153" s="0" t="inlineStr">
+      <c r="Z153" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.19444633</t>
         </is>
       </c>
-      <c r="Y153" s="0" t="inlineStr">
+      <c r="AA153" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -19801,20 +21353,30 @@
       </c>
       <c r="V154" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-04-09</t>
+        </is>
+      </c>
+      <c r="W154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X154" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.19484122; HasVersion: 10.5281/zenodo.19889377; IsPartOf: 1991-9603</t>
         </is>
       </c>
-      <c r="W154" s="0" t="inlineStr">
+      <c r="Y154" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X154" s="0" t="inlineStr">
+      <c r="Z154" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.19484121</t>
         </is>
       </c>
-      <c r="Y154" s="0" t="inlineStr">
+      <c r="AA154" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -19928,20 +21490,30 @@
       </c>
       <c r="V155" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-04-09</t>
+        </is>
+      </c>
+      <c r="W155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X155" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.19484121; IsPartOf: 1991-9603</t>
         </is>
       </c>
-      <c r="W155" s="0" t="inlineStr">
+      <c r="Y155" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X155" s="0" t="inlineStr">
+      <c r="Z155" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.19484122</t>
         </is>
       </c>
-      <c r="Y155" s="0" t="inlineStr">
+      <c r="AA155" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -20055,20 +21627,30 @@
       </c>
       <c r="V156" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="W156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X156" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.19484121; IsPartOf: 1991-9603</t>
         </is>
       </c>
-      <c r="W156" s="0" t="inlineStr">
+      <c r="Y156" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X156" s="0" t="inlineStr">
+      <c r="Z156" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.19889377</t>
         </is>
       </c>
-      <c r="Y156" s="0" t="inlineStr">
+      <c r="AA156" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -20182,20 +21764,30 @@
       </c>
       <c r="V157" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="W157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X157" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.19890222</t>
         </is>
       </c>
-      <c r="W157" s="0" t="inlineStr">
+      <c r="Y157" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X157" s="0" t="inlineStr">
+      <c r="Z157" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.19890221</t>
         </is>
       </c>
-      <c r="Y157" s="0" t="inlineStr">
+      <c r="AA157" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -20309,20 +21901,30 @@
       </c>
       <c r="V158" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-04-29</t>
+        </is>
+      </c>
+      <c r="W158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X158" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.19890221</t>
         </is>
       </c>
-      <c r="W158" s="0" t="inlineStr">
+      <c r="Y158" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X158" s="0" t="inlineStr">
+      <c r="Z158" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.19890222</t>
         </is>
       </c>
-      <c r="Y158" s="0" t="inlineStr">
+      <c r="AA158" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -20436,20 +22038,30 @@
       </c>
       <c r="V159" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="W159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X159" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.21048460</t>
         </is>
       </c>
-      <c r="W159" s="0" t="inlineStr">
+      <c r="Y159" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X159" s="0" t="inlineStr">
+      <c r="Z159" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.21048459</t>
         </is>
       </c>
-      <c r="Y159" s="0" t="inlineStr">
+      <c r="AA159" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -20563,20 +22175,30 @@
       </c>
       <c r="V160" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="W160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X160" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.21048459</t>
         </is>
       </c>
-      <c r="W160" s="0" t="inlineStr">
+      <c r="Y160" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X160" s="0" t="inlineStr">
+      <c r="Z160" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.21048460</t>
         </is>
       </c>
-      <c r="Y160" s="0" t="inlineStr">
+      <c r="AA160" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -20690,20 +22312,30 @@
       </c>
       <c r="V161" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="W161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X161" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.23044470</t>
         </is>
       </c>
-      <c r="W161" s="0" t="inlineStr">
+      <c r="Y161" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X161" s="0" t="inlineStr">
+      <c r="Z161" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.23044469</t>
         </is>
       </c>
-      <c r="Y161" s="0" t="inlineStr">
+      <c r="AA161" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -20817,20 +22449,30 @@
       </c>
       <c r="V162" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-29</t>
+        </is>
+      </c>
+      <c r="W162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X162" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.23044469</t>
         </is>
       </c>
-      <c r="W162" s="0" t="inlineStr">
+      <c r="Y162" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X162" s="0" t="inlineStr">
+      <c r="Z162" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.23044470</t>
         </is>
       </c>
-      <c r="Y162" s="0" t="inlineStr">
+      <c r="AA162" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -20944,20 +22586,30 @@
       </c>
       <c r="V163" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-10-10</t>
+        </is>
+      </c>
+      <c r="W163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X163" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasVersion: 10.5281/zenodo.23289231</t>
         </is>
       </c>
-      <c r="W163" s="0" t="inlineStr">
+      <c r="Y163" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X163" s="0" t="inlineStr">
+      <c r="Z163" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.23289230</t>
         </is>
       </c>
-      <c r="Y163" s="0" t="inlineStr">
+      <c r="AA163" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -21071,20 +22723,30 @@
       </c>
       <c r="V164" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-10-10</t>
+        </is>
+      </c>
+      <c r="W164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X164" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsVersionOf: 10.5281/zenodo.23289230</t>
         </is>
       </c>
-      <c r="W164" s="0" t="inlineStr">
+      <c r="Y164" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X164" s="0" t="inlineStr">
+      <c r="Z164" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.5281/zenodo.23289231</t>
         </is>
       </c>
-      <c r="Y164" s="0" t="inlineStr">
+      <c r="AA164" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -21198,20 +22860,30 @@
       </c>
       <c r="V165" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-01-25</t>
         </is>
       </c>
       <c r="W165" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y165" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X165" s="0" t="inlineStr">
+      <c r="Z165" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9159w</t>
         </is>
       </c>
-      <c r="Y165" s="0" t="inlineStr">
+      <c r="AA165" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -21325,20 +22997,30 @@
       </c>
       <c r="V166" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-02-28</t>
         </is>
       </c>
       <c r="W166" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y166" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X166" s="0" t="inlineStr">
+      <c r="Z166" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s93w23</t>
         </is>
       </c>
-      <c r="Y166" s="0" t="inlineStr">
+      <c r="AA166" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -21452,20 +23134,30 @@
       </c>
       <c r="V167" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-01-25</t>
         </is>
       </c>
       <c r="W167" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y167" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X167" s="0" t="inlineStr">
+      <c r="Z167" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s94w2d</t>
         </is>
       </c>
-      <c r="Y167" s="0" t="inlineStr">
+      <c r="AA167" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -21579,20 +23271,30 @@
       </c>
       <c r="V168" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-06-12</t>
         </is>
       </c>
       <c r="W168" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y168" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X168" s="0" t="inlineStr">
+      <c r="Z168" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s99g6b</t>
         </is>
       </c>
-      <c r="Y168" s="0" t="inlineStr">
+      <c r="AA168" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -21706,20 +23408,30 @@
       </c>
       <c r="V169" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-13</t>
         </is>
       </c>
       <c r="W169" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y169" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X169" s="0" t="inlineStr">
+      <c r="Z169" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9bc70</t>
         </is>
       </c>
-      <c r="Y169" s="0" t="inlineStr">
+      <c r="AA169" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -21833,20 +23545,30 @@
       </c>
       <c r="V170" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-30</t>
         </is>
       </c>
       <c r="W170" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y170" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X170" s="0" t="inlineStr">
+      <c r="Z170" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9f59m</t>
         </is>
       </c>
-      <c r="Y170" s="0" t="inlineStr">
+      <c r="AA170" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -21960,20 +23682,30 @@
       </c>
       <c r="V171" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="W171" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y171" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X171" s="0" t="inlineStr">
+      <c r="Z171" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9g015</t>
         </is>
       </c>
-      <c r="Y171" s="0" t="inlineStr">
+      <c r="AA171" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -22087,20 +23819,30 @@
       </c>
       <c r="V172" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-13</t>
         </is>
       </c>
       <c r="W172" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y172" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X172" s="0" t="inlineStr">
+      <c r="Z172" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9g59x</t>
         </is>
       </c>
-      <c r="Y172" s="0" t="inlineStr">
+      <c r="AA172" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -22214,20 +23956,30 @@
       </c>
       <c r="V173" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-30</t>
         </is>
       </c>
       <c r="W173" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y173" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X173" s="0" t="inlineStr">
+      <c r="Z173" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9k013</t>
         </is>
       </c>
-      <c r="Y173" s="0" t="inlineStr">
+      <c r="AA173" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -22341,20 +24093,30 @@
       </c>
       <c r="V174" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="W174" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y174" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X174" s="0" t="inlineStr">
+      <c r="Z174" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9ks3s</t>
         </is>
       </c>
-      <c r="Y174" s="0" t="inlineStr">
+      <c r="AA174" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -22468,20 +24230,30 @@
       </c>
       <c r="V175" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-13</t>
         </is>
       </c>
       <c r="W175" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y175" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X175" s="0" t="inlineStr">
+      <c r="Z175" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9kw2f</t>
         </is>
       </c>
-      <c r="Y175" s="0" t="inlineStr">
+      <c r="AA175" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -22595,20 +24367,30 @@
       </c>
       <c r="V176" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-30</t>
         </is>
       </c>
       <c r="W176" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y176" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X176" s="0" t="inlineStr">
+      <c r="Z176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9pp42</t>
         </is>
       </c>
-      <c r="Y176" s="0" t="inlineStr">
+      <c r="AA176" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -22722,20 +24504,30 @@
       </c>
       <c r="V177" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-13</t>
         </is>
       </c>
       <c r="W177" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y177" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X177" s="0" t="inlineStr">
+      <c r="Z177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9qp4c</t>
         </is>
       </c>
-      <c r="Y177" s="0" t="inlineStr">
+      <c r="AA177" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -22849,20 +24641,30 @@
       </c>
       <c r="V178" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-13</t>
         </is>
       </c>
       <c r="W178" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y178" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X178" s="0" t="inlineStr">
+      <c r="Z178" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9rp4p</t>
         </is>
       </c>
-      <c r="Y178" s="0" t="inlineStr">
+      <c r="AA178" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -22976,20 +24778,30 @@
       </c>
       <c r="V179" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-30</t>
         </is>
       </c>
       <c r="W179" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y179" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X179" s="0" t="inlineStr">
+      <c r="Z179" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9tg60</t>
         </is>
       </c>
-      <c r="Y179" s="0" t="inlineStr">
+      <c r="AA179" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -23103,20 +24915,30 @@
       </c>
       <c r="V180" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-13</t>
         </is>
       </c>
       <c r="W180" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y180" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X180" s="0" t="inlineStr">
+      <c r="Z180" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9vc7n</t>
         </is>
       </c>
-      <c r="Y180" s="0" t="inlineStr">
+      <c r="AA180" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -23230,20 +25052,30 @@
       </c>
       <c r="V181" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-12</t>
         </is>
       </c>
       <c r="W181" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y181" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X181" s="0" t="inlineStr">
+      <c r="Z181" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9wc7z</t>
         </is>
       </c>
-      <c r="Y181" s="0" t="inlineStr">
+      <c r="AA181" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -23357,20 +25189,30 @@
       </c>
       <c r="V182" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2024-04-29</t>
         </is>
       </c>
       <c r="W182" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y182" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X182" s="0" t="inlineStr">
+      <c r="Z182" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.57969/s9z598</t>
         </is>
       </c>
-      <c r="Y182" s="0" t="inlineStr">
+      <c r="AA182" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -23484,20 +25326,30 @@
       </c>
       <c r="V183" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-10-26</t>
         </is>
       </c>
       <c r="W183" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y183" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X183" s="0" t="inlineStr">
+      <c r="Z183" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.6084/m9.figshare.13138757</t>
         </is>
       </c>
-      <c r="Y183" s="0" t="inlineStr">
+      <c r="AA183" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -23611,20 +25463,30 @@
       </c>
       <c r="V184" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2020-10-26</t>
+        </is>
+      </c>
+      <c r="W184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X184" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsIdenticalTo: 10.6084/m9.figshare.13138757</t>
         </is>
       </c>
-      <c r="W184" s="0" t="inlineStr">
+      <c r="Y184" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X184" s="0" t="inlineStr">
+      <c r="Z184" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.6084/m9.figshare.13138757.v1</t>
         </is>
       </c>
-      <c r="Y184" s="0" t="inlineStr">
+      <c r="AA184" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -23738,20 +25600,30 @@
       </c>
       <c r="V185" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-07-12</t>
         </is>
       </c>
       <c r="W185" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y185" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X185" s="0" t="inlineStr">
+      <c r="Z185" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.6084/m9.figshare.23666259</t>
         </is>
       </c>
-      <c r="Y185" s="0" t="inlineStr">
+      <c r="AA185" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -23865,20 +25737,30 @@
       </c>
       <c r="V186" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2023-07-12</t>
+        </is>
+      </c>
+      <c r="W186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X186" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsIdenticalTo: 10.6084/m9.figshare.23666259</t>
         </is>
       </c>
-      <c r="W186" s="0" t="inlineStr">
+      <c r="Y186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X186" s="0" t="inlineStr">
+      <c r="Z186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.6084/m9.figshare.23666259.v1</t>
         </is>
       </c>
-      <c r="Y186" s="0" t="inlineStr">
+      <c r="AA186" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -23992,20 +25874,30 @@
       </c>
       <c r="V187" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-07-14</t>
         </is>
       </c>
       <c r="W187" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y187" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X187" s="0" t="inlineStr">
+      <c r="Z187" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.6084/m9.figshare.23689194</t>
         </is>
       </c>
-      <c r="Y187" s="0" t="inlineStr">
+      <c r="AA187" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -24119,20 +26011,30 @@
       </c>
       <c r="V188" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2023-12-09</t>
+        </is>
+      </c>
+      <c r="W188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X188" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">IsIdenticalTo: 10.6084/m9.figshare.23689194</t>
         </is>
       </c>
-      <c r="W188" s="0" t="inlineStr">
+      <c r="Y188" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X188" s="0" t="inlineStr">
+      <c r="Z188" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.6084/m9.figshare.23689194.v1</t>
         </is>
       </c>
-      <c r="Y188" s="0" t="inlineStr">
+      <c r="AA188" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
@@ -24246,27 +26148,37 @@
       </c>
       <c r="V189" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">2021-01-15</t>
+        </is>
+      </c>
+      <c r="W189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REACH office Pub Date: DataCite created (reviewer may edit)</t>
+        </is>
+      </c>
+      <c r="X189" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/6m311p67k; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/8049g5303; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/bg257f30t; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/pc289j45z; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/0r967395n; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/79407x487; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/pc289j467; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/wh246s349; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/b5644r801; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/n009w265m; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/z603qx64j; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/v979v339k; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/mp48sd042; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/sj139226h; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/qf85nb53h; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/xp68kg42c; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/2z10wq458; HasPart: https://deepblue.lib.umich.edu/data/concern/file_sets/b8515n63m</t>
         </is>
       </c>
-      <c r="W189" s="0" t="inlineStr">
+      <c r="Y189" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">live</t>
         </is>
       </c>
-      <c r="X189" s="0" t="inlineStr">
+      <c r="Z189" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://api.datacite.org/dois/10.7302/y2qt-7f47</t>
         </is>
       </c>
-      <c r="Y189" s="0" t="inlineStr">
+      <c r="AA189" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">api-discoveries/historical/batches/2026-10-28-historical-datacite-spark-all-part002.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y189"/>
+  <autoFilter ref="A1:AA189"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24782,17 +26694,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date Category</t>
+          <t xml:space="preserve">Evidence Category</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suggested Date</t>
+          <t xml:space="preserve">Alternative Date</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why Reviewer Should Check</t>
+          <t xml:space="preserve">Evidence Detail (informational only)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -31205,149 +33117,161 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structured date pending</t>
+          <t xml:space="preserve">REACH Pub Date (DataCite created)</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typed DataCite Issued or Available full date exists, but independent native DOI-level evidence was not extracted. The candidate is not auto-published.</t>
+          <t xml:space="preserve">Office-approved complete Pub Date for DataCite DOI: use YYYY-MM-DD from created without requiring independent date corroboration, acknowledgment or date-only human referral. Reviewer may edit normally before authorized insertion.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provisional Date</t>
+          <t xml:space="preserve">Structured date evidence</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DataCite created/registered is NOT first publication; it is just a suggested date to compare with native source. Dates can predate repository publication.</t>
+          <t xml:space="preserve">Typed Issued/Available date may differ from DataCite created, but this does NOT make the REACH Pub Date missing under WPO policy. Keep differences as optional provenance.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Publication Year</t>
+          <t xml:space="preserve">Date meaning</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retain 2025 as 2025 when exact month/day is not confirmed. Never synthesize 2025-01-01.</t>
+          <t xml:space="preserve">DataCite created is the date of DOI metadata-record creation. The office knowingly accepts its calendar date as Pub Date; the value is not a claim about first public release.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DataCite Published</t>
+          <t xml:space="preserve">Publication Year</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">May be a year-only value; based on Issued date if present, otherwise publicationYear (DataCite documentation).</t>
+          <t xml:space="preserve">Retain 2025 as 2025 when exact month/day is not confirmed. Never synthesize 2025-01-01.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Native checks</t>
+          <t xml:space="preserve">DataCite Published</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read only allowlisted repository HTML; only DOI-matched citation metadata or DOI-specific JSON-LD date counts. Dynamic pages, login barriers and API-only landing pages remain unresolved.</t>
+          <t xml:space="preserve">May be a year-only value; based on Issued date if present, otherwise publicationYear (DataCite documentation).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conflicts</t>
+          <t xml:space="preserve">Native checks</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Different full Issued/Available dates can be reasonable, e.g. embargo; never silently pick earliest or latest. Version DOI relationships also require review.</t>
+          <t xml:space="preserve">Read only allowlisted repository HTML; only DOI-matched citation metadata or DOI-specific JSON-LD date counts. Dynamic pages, login barriers and API-only landing pages remain unresolved.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date types</t>
+          <t xml:space="preserve">Conflicts</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">An observation-period, submission, acceptance, last-updated or DOI registration date is not a substitute for the first public release.</t>
+          <t xml:space="preserve">Alternative Issued/Available dates are retained as supplemental information, not automatic date-blocker flags. DOI version/identity uncertainty still needs separate review.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Original catalog metadata</t>
+          <t xml:space="preserve">Date types</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Title, output type, award and parent are taken from the original checksum-verified DataCite intake; no overwrites.</t>
+          <t xml:space="preserve">An observation-period, submission, acceptance, last-updated or DOI registration date is not a substitute for the first public release.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reviewer action</t>
+          <t xml:space="preserve">Original catalog metadata</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">This sheet is evidence for Scout or a human reviewer, not a Discovery Hub intake, decision, Smartsheet update or REACH publication.</t>
+          <t xml:space="preserve">Title, output type, award and parent are taken from the original checksum-verified DataCite intake; no overwrites.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">API failure</t>
+          <t xml:space="preserve">Reviewer action</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failed fetch is shown explicitly. A previously successful snapshot is retained with an access-failure note, not described as a live result.</t>
+          <t xml:space="preserve">This sheet is evidence for Scout or a human reviewer, not a Discovery Hub intake, decision, Smartsheet update or REACH publication.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DesignSafe example</t>
+          <t xml:space="preserve">API failure</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.17603/ds2-58ft-kp27: compare created 2025-04-10 with a verified DesignSafe publication date and exact version; the existing parent reach-000816 raises an independent duplicate/eligibility question.</t>
+          <t xml:space="preserve">Failed fetch is shown explicitly. A previously successful snapshot is retained with an access-failure note, not described as a live result.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">DesignSafe example</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.17603/ds2-58ft-kp27: compare created 2025-04-10 with a verified DesignSafe publication date and exact version; the existing parent reach-000816 raises an independent duplicate/eligibility question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">Source docs</t>
         </is>
       </c>
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">https://support.datacite.org/docs/what-is-the-difference-between-the-created-and-registered-date-in-the-datacite-rest-api</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B14"/>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
 </file>